--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedSupportingInfoSonderklasse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
